--- a/prompts/Contextual_Form_WI.xlsx
+++ b/prompts/Contextual_Form_WI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/edgardomosesezekielaverilla/Documents/Documents - Edgardo’s MacBook Air/Projects/AiDA-Documentation-Agent/prompts/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D30DDEBB-FAE1-B740-8480-06D74DE86699}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25777344-A1E1-174D-B834-22DB21B8A218}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="26460" windowHeight="19120" xr2:uid="{E3E65FFB-6B3D-2846-B138-AECE72D99295}"/>
+    <workbookView xWindow="-22240" yWindow="600" windowWidth="22240" windowHeight="14800" xr2:uid="{E3E65FFB-6B3D-2846-B138-AECE72D99295}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -53,9 +53,6 @@
     <t>Purpose</t>
   </si>
   <si>
-    <t>Prompt: "If provided, rephrase into 1-2 concise sentences. If blank, infer from Title and related SOP, then append: 'Review required: Purpose statement generated without user input.'"</t>
-  </si>
-  <si>
     <t>2. Scope</t>
   </si>
   <si>
@@ -68,36 +65,84 @@
     <t>Systems Involved</t>
   </si>
   <si>
-    <t>Prompt: If entries are present, list each team or region clearly. If blank, insert placeholder text: 'Team/region aplpicability pending confirmation by author.' Do not assume or generate department names."</t>
-  </si>
-  <si>
-    <t>Prompt: "If blank, infer from Title and Purpose; append 'Review required: task description generated without user input.'"</t>
-  </si>
-  <si>
-    <t>Prompt "If system information is provided, structure into a two-column table ("System/Tool',
-*Purpose'). If not provided, infer likely systems based on [Process Name] context (e.g., CRM, Workday, ServiceNow), add short neutral descriptions, and append: A Review required: system list generated based on contextual inference.' Example output: \n</t>
-  </si>
-  <si>
     <t>3. Procedure Table</t>
   </si>
   <si>
-    <t>Step No. + Action</t>
-  </si>
-  <si>
-    <t>"If steps are provided in numerical format, retain and refine each action into clear, imperative sentences.
-If descriptive, convert into numbered steps.
-If supplementary documents are uploaded (e.g., video transcripts in Taglish/English, system templates, screenshots, SOPs), extract step-by-step actions directly from those materials.
-Translate informal or code-switched language into formal, task-focused English aligned with JLL standards.
-Format as a table with columns: Step No., Action, Screenshot Placeholder, Notes.
-Extract as many steps as necessary to fully represent the task - do not artificially limit the number of steps. Each distinct action should be its own row.
-If blank and no supplementary materials are available, infer logical steps from Title, Purpose, and System/Tool based on typical workflows.
-Append:
-A Review required: procedure steps generated without user input.
-Example output:
-Step No. | Action | Screenshot | Notes |
-| 1 | Open [System] and navigate to [Module] | (Placeholder) | Ensure correct credentials |
-| 2 | Enter required data in [Field Name] |
-(Placeholder) | Refer to data validation rules | | 3 | Click 'Submit' and verify confirmation message | (Placeholder) | Confirmation ID should appear |”</t>
+    <t>Step No. + Action 
+(procedure Table)</t>
+  </si>
+  <si>
+    <t>If provided:
+Rephrase into 1–2 concise sentences while preserving the original intent.
+If blank:
+Infer the purpose from the document title, uploaded transcripts, reference documents, and supporting materials.
+If confidence is low:
+Insert: "Review required: Purpose statement could not be inferred from available source materials."
+Output Requirements:
+Use clear and professional business language.
+Focus on the objective or outcome of the process.
+Avoid implementation details or procedural steps.</t>
+  </si>
+  <si>
+    <t>If provided:
+List each applicable team, function, region, or audience clearly and consistently.
+If blank:
+Identify applicable groups from uploaded transcripts, reference documents, and supporting materials.
+If confidence is low:
+Insert: "Review required: Applicability could not be determined from available source materials."
+Output Requirements:
+Present as a bulleted list or structured table.
+Do not invent department, team, or region names.
+Only include groups explicitly referenced or strongly supported by source materials.</t>
+  </si>
+  <si>
+    <t>If provided:
+Refine the task description into a concise statement describing the activity being performed.
+If blank:
+Infer the task from the document title, purpose statement, uploaded transcripts, and supporting materials.
+If confidence is low:
+Insert: "Review required: Task description could not be determined from available source materials."
+Output Requirements:
+Use a short, action-oriented description.
+Clearly describe the activity without procedural detail.
+Focus on the business activity rather than the system used.</t>
+  </si>
+  <si>
+    <t>If provided:
+Organize the information into a two-column table with columns: System/Tool and Purpose.
+If blank:
+Identify systems, applications, platforms, or tools referenced in uploaded transcripts, screenshots, reference documents, and supporting materials.
+If confidence is low:
+Insert: "Review required: Systems involved could not be determined from available source materials."
+Output Requirements:
+Present as a table with columns: System/Tool and Purpose.
+Provide a concise purpose statement for each system identified.
+Do not invent system names that are not supported by source materials.</t>
+  </si>
+  <si>
+    <t>If provided:
+Retain the procedural sequence and rewrite actions as clear, concise, imperative instructions.
+If blank:
+Extract procedural steps from uploaded transcripts, videos, screenshots, templates, reference documents, and supporting materials.
+If confidence is low:
+Insert: "Review required: One or more procedural steps could not be determined from available source materials."
+Output Requirements:
+Preserve the original sequence of activities.
+Convert descriptive narratives into numbered procedural steps.
+Translate informal language into professional, task-focused English.
+Create one row per distinct action.
+Do not combine multiple actions into a single step.
+Generate as many steps as necessary to fully represent the process.
+Present output as a table with columns:
+Step No.
+Action
+Screenshot Placeholder
+Notes
+Example Format:
+Step No.	Action	Screenshot Placeholder	Notes
+1	Open the required system and navigate to the appropriate module.	(Placeholder)	Verify access permissions.
+2	Enter the required information into the designated fields.	(Placeholder)	Validate all required data before proceeding.
+3	Submit the transaction and verify successful completion.	(Placeholder)	Confirm that a reference number or confirmation message is generated.</t>
   </si>
 </sst>
 </file>
@@ -139,7 +184,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -148,11 +193,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -529,19 +580,19 @@
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -573,55 +624,55 @@
     </row>
     <row r="9" spans="1:10" ht="93" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
     </row>
     <row r="10" spans="1:10" ht="93" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="6"/>
     </row>
     <row r="11" spans="1:10" ht="111" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -652,23 +703,43 @@
       <c r="J15" s="2"/>
     </row>
     <row r="16" spans="1:10" ht="400" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="3" t="s">
-        <v>14</v>
+      <c r="A16" s="5" t="s">
+        <v>10</v>
       </c>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="4" t="s">
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
-      <c r="J16" s="4"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
+      <c r="J16" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="G3:J3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="G4:J4"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="G8:J8"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="G9:J9"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="G10:J10"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="G11:J11"/>
     <mergeCell ref="A13:J13"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="D15:F15"/>
@@ -676,26 +747,6 @@
     <mergeCell ref="A16:C16"/>
     <mergeCell ref="D16:F16"/>
     <mergeCell ref="G16:J16"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="G10:J10"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="G11:J11"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="G8:J8"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="G9:J9"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="D3:F3"/>
-    <mergeCell ref="G3:J3"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="D4:F4"/>
-    <mergeCell ref="G4:J4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
